--- a/GELSIGHT_OPPORTUNITIES.xlsx
+++ b/GELSIGHT_OPPORTUNITIES.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,6 +424,11 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Matched Keyword</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>

--- a/GELSIGHT_OPPORTUNITIES.xlsx
+++ b/GELSIGHT_OPPORTUNITIES.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,6 +430,197 @@
       <c r="C1" t="inlineStr">
         <is>
           <t>Title</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Solicitation Number</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Department/Agency</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Base Type</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Posted Date</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Response Deadline</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NAICS Code</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Classification Code</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Set Aside</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Office City</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Office State</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Office ZIP</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Contact Email</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Contact Phone</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Description Link</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>UI Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>9ee8339fc69041ac9e55449e7e254bb0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>elastomeric</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>31--BEARING,ELASTOMERIC</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SPE4A626T17ZE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>DEPT OF DEFENSE.DEFENSE LOGISTICS AGENCY.DLA AVIATION.DLA AV RICHMOND.DLA AVIATION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Combined Synopsis/Solicitation</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Combined Synopsis/Solicitation</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>332991</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>RICHMOND</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>23237</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions regarding this solicitation should be emailed to the buyer listed in block 5 of the solicitation document which can be found under the Additional Information link.
+If the Additional Information link does not work, please go to https://www.dibbs.bsm.dla.mil/Solicitations/ and type the solicitation number in the Global Search box.
+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>DibbsBSM@dla.mil</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>https://api.sam.gov/prod/opportunities/v1/noticedesc?noticeid=9ee8339fc69041ac9e55449e7e254bb0</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://sam.gov/workspace/contract/opp/9ee8339fc69041ac9e55449e7e254bb0/view</t>
         </is>
       </c>
     </row>

--- a/GELSIGHT_OPPORTUNITIES.xlsx
+++ b/GELSIGHT_OPPORTUNITIES.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U2"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,197 +432,6 @@
           <t>Title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Solicitation Number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Department/Agency</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Base Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Posted Date</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response Deadline</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>NAICS Code</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Classification Code</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Set Aside</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Office City</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Office State</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Office ZIP</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Contact Name</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Contact Email</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>Contact Phone</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>Description Link</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>UI Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>9ee8339fc69041ac9e55449e7e254bb0</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>elastomeric</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>31--BEARING,ELASTOMERIC</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SPE4A626T17ZE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>DEPT OF DEFENSE.DEFENSE LOGISTICS AGENCY.DLA AVIATION.DLA AV RICHMOND.DLA AVIATION</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Combined Synopsis/Solicitation</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Combined Synopsis/Solicitation</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>332991</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>RICHMOND</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>23237</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Questions regarding this solicitation should be emailed to the buyer listed in block 5 of the solicitation document which can be found under the Additional Information link.
-If the Additional Information link does not work, please go to https://www.dibbs.bsm.dla.mil/Solicitations/ and type the solicitation number in the Global Search box.
-</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>DibbsBSM@dla.mil</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>https://api.sam.gov/prod/opportunities/v1/noticedesc?noticeid=9ee8339fc69041ac9e55449e7e254bb0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>https://sam.gov/workspace/contract/opp/9ee8339fc69041ac9e55449e7e254bb0/view</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
